--- a/Project/DiceWarrior/LubanTool/Datas/EventCard.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/EventCard.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -41,19 +41,43 @@
     <t>desc</t>
   </si>
   <si>
+    <t>spriteName</t>
+  </si>
+  <si>
+    <t>enabled</t>
+  </si>
+  <si>
+    <t>DiceEnhanceId</t>
+  </si>
+  <si>
+    <t>DrawWeight</t>
+  </si>
+  <si>
+    <t>repeatable</t>
+  </si>
+  <si>
+    <t>mutexGroup</t>
+  </si>
+  <si>
+    <t>fixedOrder</t>
+  </si>
+  <si>
+    <t>availableLayers</t>
+  </si>
+  <si>
     <t>cardType</t>
   </si>
   <si>
-    <t>battleId</t>
-  </si>
-  <si>
-    <t>drawWeight</t>
-  </si>
-  <si>
-    <t>spriteName</t>
-  </si>
-  <si>
-    <t>enabled</t>
+    <t>eventType</t>
+  </si>
+  <si>
+    <t>enemyList</t>
+  </si>
+  <si>
+    <t>rewardList</t>
+  </si>
+  <si>
+    <t>poolCondition</t>
   </si>
   <si>
     <t>##type</t>
@@ -65,100 +89,180 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>eventcard.EEventCardType</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>遭遇战</t>
-  </si>
-  <si>
-    <t>战斗事件，占位效果。</t>
-  </si>
-  <si>
-    <t>Battle</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>精英拦路</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>突袭</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>岔路口</t>
-  </si>
-  <si>
-    <t>中立事件，占位效果。</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>神秘商人</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>休整营地</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>普通宝箱</t>
-  </si>
-  <si>
-    <t>宝箱事件，占位效果。</t>
-  </si>
-  <si>
-    <t>Treasure</t>
-  </si>
-  <si>
-    <t>3002</t>
-  </si>
-  <si>
-    <t>稀有宝箱</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>强化ID</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>可重复</t>
+  </si>
+  <si>
+    <t>互斥组</t>
+  </si>
+  <si>
+    <t>重新开始固定排序</t>
+  </si>
+  <si>
+    <t>会出现的层数</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>敌人列表</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>进事件池条件</t>
+  </si>
+  <si>
+    <t>1层测试战斗</t>
+  </si>
+  <si>
+    <t>战斗</t>
+  </si>
+  <si>
+    <t>100 50 20 5</t>
+  </si>
+  <si>
+    <t>2层测试战斗</t>
+  </si>
+  <si>
+    <t>3层测试战斗</t>
+  </si>
+  <si>
+    <t>1层boss1</t>
+  </si>
+  <si>
+    <t>如果楼梯没有出现，战斗后的下一张牌一定是楼梯</t>
+  </si>
+  <si>
+    <t>0 0 2 1</t>
+  </si>
+  <si>
+    <t>1层boss2</t>
+  </si>
+  <si>
+    <t>2层boss1</t>
+  </si>
+  <si>
+    <t>2层boss2</t>
+  </si>
+  <si>
+    <t>3层boss1</t>
+  </si>
+  <si>
+    <t>胜利后游戏结束</t>
+  </si>
+  <si>
+    <t>3层boss2</t>
+  </si>
+  <si>
+    <t>巨人</t>
+  </si>
+  <si>
+    <t>无法战胜的战斗</t>
+  </si>
+  <si>
+    <t>数据表1为1</t>
+  </si>
+  <si>
+    <t>巨人2</t>
+  </si>
+  <si>
+    <t>毒沼</t>
+  </si>
+  <si>
+    <t>通过时损失掉血</t>
+  </si>
+  <si>
+    <t>恶意</t>
+  </si>
+  <si>
+    <t>诅咒丛林</t>
+  </si>
+  <si>
+    <t>通过时获得随机诅咒</t>
+  </si>
+  <si>
+    <t>神秘旅人</t>
+  </si>
+  <si>
+    <t>判定坏，进战斗，判定好得道具。</t>
+  </si>
+  <si>
+    <t>中立</t>
+  </si>
+  <si>
+    <t>蘑菇</t>
+  </si>
+  <si>
+    <t>判定坏，掉血，判断好回血。</t>
+  </si>
+  <si>
+    <t>废弃祭坛</t>
+  </si>
+  <si>
+    <t>获得一个随机道具。</t>
+  </si>
+  <si>
+    <t>友好</t>
+  </si>
+  <si>
+    <t>祭坛</t>
+  </si>
+  <si>
+    <t>获得一个全新的骰子。或者支付钱获得更稀有的全新的骰子。</t>
+  </si>
+  <si>
+    <t>诅咒祭坛</t>
+  </si>
+  <si>
+    <t>选择一个骰子，丢弃其他所有的骰子，
+选择的这个骰子的复制品将填满其他骰子的空位槽。
+所有骰子无法附魔，也无法丢弃。</t>
+  </si>
+  <si>
+    <t>楼梯</t>
+  </si>
+  <si>
+    <t>前往下一层</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>门</t>
+  </si>
+  <si>
+    <t>阻挡了前进的路</t>
+  </si>
+  <si>
+    <t>神秘祭坛</t>
+  </si>
+  <si>
+    <t>玩家取走祭坛遗物后，局外获得初始骰子。</t>
+  </si>
+  <si>
+    <t>数据表1为0</t>
   </si>
 </sst>
 </file>
@@ -950,11 +1054,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -991,13 +1098,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1319,317 +1429,1049 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.9166666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.83333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.8333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.91666666666667" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.8333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="55.6666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.1666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.91666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.0833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.0833333333333" style="2" customWidth="1"/>
+    <col min="9" max="10" width="10.8333333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.9166666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1666666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.8333333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="13.9166666666667" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" customHeight="1" spans="1:17">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:17">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
       <c r="I2" s="7"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>11</v>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="8"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:17">
+      <c r="A3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:17">
+      <c r="A4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="13"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="8" t="s">
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:17">
+      <c r="A5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:17">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13">
+        <v>10001</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13">
+        <v>100</v>
+      </c>
+      <c r="I6" s="13">
+        <v>1</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13">
+        <v>1</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="13">
+        <v>1</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:17">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10">
+        <v>10002</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10">
+        <v>100</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10">
+        <v>2</v>
+      </c>
+      <c r="M7" s="13">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="10">
+        <v>2</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="11"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:17">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13">
+        <v>10003</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13">
+        <v>100</v>
+      </c>
+      <c r="I8" s="13">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13">
+        <v>3</v>
+      </c>
+      <c r="M8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" s="13">
+        <v>3</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:17">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10">
+        <v>20001</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13">
+        <v>1</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" s="10">
+        <v>1001</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="11"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:17">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13">
+        <v>20002</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>1</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" s="13">
+        <v>1001</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:17">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10">
+        <v>20003</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10">
+        <v>2</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10">
+        <v>2</v>
+      </c>
+      <c r="M11" s="13">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="10">
+        <v>1001</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="11"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:17">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13">
+        <v>20004</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
+        <v>2</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13">
+        <v>2</v>
+      </c>
+      <c r="M12" s="13">
+        <v>1</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O12" s="13">
+        <v>1001</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:17">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10">
+        <v>20005</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10">
+        <v>3</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10">
+        <v>3</v>
+      </c>
+      <c r="M13" s="13">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O13" s="10">
+        <v>1001</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="11"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:17">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13">
+        <v>20006</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>3</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13">
+        <v>3</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14" s="13">
+        <v>1001</v>
+      </c>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:17">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10">
+        <v>20007</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10">
+        <v>1</v>
+      </c>
+      <c r="M15" s="13">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" s="10">
+        <v>9001</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:17">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13">
+        <v>20008</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13">
+        <v>1</v>
+      </c>
+      <c r="M16" s="13">
+        <v>1</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O16" s="13">
+        <v>9001</v>
+      </c>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:17">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10">
+        <v>30001</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10">
+        <v>100</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="13">
+        <v>1</v>
+      </c>
+      <c r="M17" s="10">
+        <v>4</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="11"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:17">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13">
+        <v>30002</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13">
+        <v>100</v>
+      </c>
+      <c r="I18" s="13">
+        <v>1</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13">
+        <v>1</v>
+      </c>
+      <c r="M18" s="13">
+        <v>4</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:17">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10">
+        <v>4</v>
+      </c>
+      <c r="H19" s="10">
+        <v>100</v>
+      </c>
+      <c r="I19" s="10">
+        <v>1</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="13">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10">
+        <v>2</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="11"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:17">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13">
+        <v>40002</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13">
+        <v>100</v>
+      </c>
+      <c r="I20" s="13">
+        <v>1</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="10">
+        <v>2</v>
+      </c>
+      <c r="M20" s="13">
+        <v>2</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:17">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10">
+        <v>50001</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="13">
+        <v>2</v>
+      </c>
+      <c r="M21" s="10">
+        <v>5</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="11"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:17">
+      <c r="A22" s="12"/>
+      <c r="B22" s="13">
+        <v>50002</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="13">
+        <v>4</v>
+      </c>
+      <c r="H22" s="13">
+        <v>100</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="10">
+        <v>2</v>
+      </c>
+      <c r="M22" s="13">
+        <v>5</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" ht="61" customHeight="1" spans="1:17">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10">
+        <v>50003</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10">
+        <v>100</v>
+      </c>
+      <c r="I23" s="10">
+        <v>0</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="13">
+        <v>2</v>
+      </c>
+      <c r="M23" s="10">
+        <v>5</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="11"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:17">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13">
+        <v>90001</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13">
+        <v>0</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13">
         <v>15</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="13"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="13"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="16"/>
+      <c r="L24" s="10">
+        <v>2</v>
+      </c>
+      <c r="M24" s="13">
+        <v>6</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:17">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10">
+        <v>90002</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10">
+        <v>0</v>
+      </c>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="13">
+        <v>3</v>
+      </c>
+      <c r="M25" s="10">
+        <v>6</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="11"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:17">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17">
+        <v>91001</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17">
+        <v>4</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17">
+        <v>1</v>
+      </c>
+      <c r="M26" s="17">
+        <v>6</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="18" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Project/DiceWarrior/LubanTool/Datas/EventCard.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/EventCard.xlsx
@@ -2271,7 +2271,7 @@
         <v>-1</v>
       </c>
       <c r="I21" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -2310,7 +2310,7 @@
         <v>100</v>
       </c>
       <c r="I22" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
@@ -2347,7 +2347,7 @@
         <v>100</v>
       </c>
       <c r="I23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -2455,7 +2455,9 @@
         <v>4</v>
       </c>
       <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
+      <c r="I26" s="17">
+        <v>0</v>
+      </c>
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17">

--- a/Project/DiceWarrior/LubanTool/Datas/EventCard.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/EventCard.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,9 @@
     <t>eventcard.EEventCardType</t>
   </si>
   <si>
+    <t>(map#sep=|,),int,int</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -128,7 +131,7 @@
     <t>敌人列表</t>
   </si>
   <si>
-    <t>奖励</t>
+    <t>奖励表ID和权重</t>
   </si>
   <si>
     <t>进事件池条件</t>
@@ -140,7 +143,7 @@
     <t>战斗</t>
   </si>
   <si>
-    <t>100 50 20 5</t>
+    <t>1|100,2|50,1001|20</t>
   </si>
   <si>
     <t>2层测试战斗</t>
@@ -153,9 +156,6 @@
   </si>
   <si>
     <t>如果楼梯没有出现，战斗后的下一张牌一定是楼梯</t>
-  </si>
-  <si>
-    <t>0 0 2 1</t>
   </si>
   <si>
     <t>1层boss2</t>
@@ -1435,18 +1435,18 @@
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.8333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="55.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="11.1666666666667" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.91666666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.0833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.0833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.8333333333333" style="2" customWidth="1"/>
     <col min="9" max="10" width="10.8333333333333" style="2" customWidth="1"/>
     <col min="11" max="11" width="17.75" style="2" customWidth="1"/>
     <col min="12" max="12" width="15.9166666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="25.75" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.1666666666667" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.8333333333333" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.5" style="2" customWidth="1"/>
+    <col min="16" max="16" width="36.5833333333333" style="2" customWidth="1"/>
     <col min="17" max="17" width="13.9166666666667" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
@@ -1572,7 +1572,7 @@
         <v>19</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>19</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1601,45 +1601,45 @@
     </row>
     <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:17">
@@ -1648,10 +1648,10 @@
         <v>10001</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="b">
@@ -1673,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O6" s="13">
         <v>1</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q6" s="14"/>
     </row>
@@ -1689,10 +1689,10 @@
         <v>10002</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="13" t="b">
@@ -1714,13 +1714,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O7" s="10">
         <v>2</v>
       </c>
-      <c r="P7" s="10" t="s">
-        <v>37</v>
+      <c r="P7" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="Q7" s="11"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>10003</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13" t="b">
@@ -1755,13 +1755,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O8" s="13">
         <v>3</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="14"/>
     </row>
@@ -1771,10 +1771,10 @@
         <v>20001</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="13" t="b">
@@ -1798,13 +1798,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O9" s="10">
         <v>1001</v>
       </c>
-      <c r="P9" s="10" t="s">
-        <v>42</v>
+      <c r="P9" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="Q9" s="11"/>
     </row>
@@ -1817,7 +1817,7 @@
         <v>43</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="b">
@@ -1841,13 +1841,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O10" s="13">
         <v>1001</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q10" s="14"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="13" t="b">
@@ -1884,13 +1884,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O11" s="10">
         <v>1001</v>
       </c>
-      <c r="P11" s="10" t="s">
-        <v>42</v>
+      <c r="P11" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="Q11" s="11"/>
     </row>
@@ -1903,7 +1903,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="13" t="b">
@@ -1927,13 +1927,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O12" s="13">
         <v>1001</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="14"/>
     </row>
@@ -1970,12 +1970,14 @@
         <v>1</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O13" s="10">
         <v>1001</v>
       </c>
-      <c r="P13" s="10"/>
+      <c r="P13" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q13" s="11"/>
     </row>
     <row r="14" customHeight="1" spans="1:17">
@@ -2011,12 +2013,14 @@
         <v>1</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O14" s="13">
         <v>1001</v>
       </c>
-      <c r="P14" s="13"/>
+      <c r="P14" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q14" s="14"/>
     </row>
     <row r="15" customHeight="1" spans="1:17">
@@ -2050,12 +2054,14 @@
         <v>1</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O15" s="10">
         <v>9001</v>
       </c>
-      <c r="P15" s="10"/>
+      <c r="P15" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q15" s="11" t="s">
         <v>51</v>
       </c>
@@ -2091,12 +2097,14 @@
         <v>1</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O16" s="13">
         <v>9001</v>
       </c>
-      <c r="P16" s="13"/>
+      <c r="P16" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q16" s="14" t="s">
         <v>51</v>
       </c>
@@ -2135,7 +2143,9 @@
         <v>55</v>
       </c>
       <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
+      <c r="P17" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q17" s="11"/>
     </row>
     <row r="18" customHeight="1" spans="1:17">
@@ -2172,7 +2182,9 @@
         <v>55</v>
       </c>
       <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
+      <c r="P18" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q18" s="14"/>
     </row>
     <row r="19" customHeight="1" spans="1:17">
@@ -2211,7 +2223,9 @@
         <v>60</v>
       </c>
       <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
+      <c r="P19" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q19" s="11"/>
     </row>
     <row r="20" customHeight="1" spans="1:17">
@@ -2248,7 +2262,9 @@
         <v>60</v>
       </c>
       <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
+      <c r="P20" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q20" s="14"/>
     </row>
     <row r="21" customHeight="1" spans="1:17">
@@ -2285,7 +2301,9 @@
         <v>65</v>
       </c>
       <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
+      <c r="P21" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q21" s="11"/>
     </row>
     <row r="22" customHeight="1" spans="1:17">
@@ -2324,7 +2342,9 @@
         <v>65</v>
       </c>
       <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
+      <c r="P22" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q22" s="14"/>
     </row>
     <row r="23" ht="61" customHeight="1" spans="1:17">
@@ -2361,7 +2381,9 @@
         <v>65</v>
       </c>
       <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
+      <c r="P23" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q23" s="11"/>
     </row>
     <row r="24" customHeight="1" spans="1:17">
@@ -2398,7 +2420,9 @@
         <v>72</v>
       </c>
       <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
+      <c r="P24" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q24" s="14"/>
     </row>
     <row r="25" customHeight="1" spans="1:17">
@@ -2433,7 +2457,9 @@
         <v>72</v>
       </c>
       <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
+      <c r="P25" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q25" s="11"/>
     </row>
     <row r="26" customHeight="1" spans="1:17">
@@ -2470,7 +2496,9 @@
         <v>72</v>
       </c>
       <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
+      <c r="P26" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="Q26" s="18" t="s">
         <v>77</v>
       </c>
